--- a/app3/template.xlsx
+++ b/app3/template.xlsx
@@ -557,16 +557,17 @@
 • Форма обучения: Очная                                                                                                    • Стоимость: 90 500 ₽/год</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Паспорт
-2. Аттестат
-3. 4 фото
-4. Медсправка 086
-5. Прививочный сертификат
-6. Полис
-7. СНИЛС
-8. ИНН
-9. Льготы
-10. Приписное</t>
+    <t xml:space="preserve">1. Паспорт + копия (страница с фото и прописка)
+2. Аттестат (оригинал/заверенная копия)
+3. Фото 3×4 — 4 шт
+4. Заключение медицинского осмотра
+5. СНИЛС (2 копии)
+6. Прививочный сертификат
+7. Медицинский полис (2 копии)
+8. Документы об инвалидности/ОВЗ
+9. Заключение ПМПК (для лиц с ОВЗ)
+10. Документы подтверждающие социальный статус
+11. Документы подтверждающие индивидуальные достижения</t>
   </si>
   <si>
     <t xml:space="preserve">г. Талица, ул. Луначарского, д. 81, кабинет 1.
@@ -617,7 +618,7 @@
         <family val="2"/>
         <charset val="204"/>
       </rPr>
-      <t xml:space="preserve">Какие документы нужны для поступления?
+      <t xml:space="preserve">Какие документы нужны для поступления? Перечень документов для поступления
 </t>
     </r>
     <r>
@@ -631,26 +632,14 @@
       <t xml:space="preserve">1. Паспорт + копия (страница с фото и прописка)
 2. Аттестат (оригинал/заверенная копия)
 3. Фото 3×4 — 4 шт
-4. Медсправка 086 (с флюорографией за 2024 г.)
+4. Заключение медицинского осмотра
 5. СНИЛС (2 копии)
 6. Прививочный сертификат
 7. Медицинский полис (2 копии)
 8. Документы об инвалидности/ОВЗ
 9. Заключение ПМПК (для лиц с ОВЗ)
-10. Документы о льготах
-11. ИНН (копия)
-📌</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> Подробнее в разделе "Документы"
+10. Документы подтверждающие социальный статус
+11. Документы подтверждающие индивидуальные достижения
 </t>
     </r>
     <r>
@@ -857,7 +846,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -874,11 +863,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -895,7 +888,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -907,14 +900,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF548235"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -2114,7 +2099,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="127.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
         <v>51</v>
       </c>
@@ -2127,7 +2112,7 @@
       <c r="D57" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E57" s="3" t="s">
+      <c r="E57" s="4" t="s">
         <v>106</v>
       </c>
     </row>
@@ -2186,16 +2171,16 @@
       <c r="A61" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="B61" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C61" s="4" t="s">
+      <c r="C61" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D61" s="4" t="s">
+      <c r="D61" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E61" s="5" t="s">
+      <c r="E61" s="6" t="s">
         <v>111</v>
       </c>
     </row>
@@ -2203,12 +2188,12 @@
       <c r="A62" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="C62" s="4"/>
-      <c r="D62" s="4"/>
-      <c r="E62" s="6" t="s">
+      <c r="C62" s="5"/>
+      <c r="D62" s="5"/>
+      <c r="E62" s="7" t="s">
         <v>113</v>
       </c>
     </row>
